--- a/03_homework/Disney_raw.xlsx
+++ b/03_homework/Disney_raw.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{24396BC2-83D5-DC46-A78A-092B16A8738C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="580" windowWidth="28800" windowHeight="18060" xr2:uid="{9B187DEB-297A-804A-94EF-DD6798B181AE}"/>
+    <workbookView xWindow="13120" yWindow="580" windowWidth="15300" windowHeight="16760" xr2:uid="{9B187DEB-297A-804A-94EF-DD6798B181AE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
